--- a/tools/importer/reports/import-research-facilities.report.xlsx
+++ b/tools/importer/reports/import-research-facilities.report.xlsx
@@ -97,7 +97,7 @@
     <t>programs</t>
   </si>
   <si>
-    <t>2026-10-29T00:49:24.817Z</t>
+    <t>2026-10-29T01:19:49.954Z</t>
   </si>
   <si>
     <t>https://www.sfu.ca/beedie/programs/undergraduate/bba-major/program.html</t>
@@ -139,7 +139,7 @@
     <t>resources</t>
   </si>
   <si>
-    <t>2026-10-29T01:00:14.429Z</t>
+    <t>2026-10-29T01:20:07.922Z</t>
   </si>
   <si>
     <t>templates/landing-page.report.json</t>
@@ -163,7 +163,7 @@
     <t>programs-template</t>
   </si>
   <si>
-    <t>2026-10-29T00:49:33.239Z</t>
+    <t>2026-10-29T01:19:59.428Z</t>
   </si>
   <si>
     <t>templates/resources.report.json</t>
